--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486451_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486451_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0663</v>
+        <v>3.4643</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4241</v>
+        <v>1.822</v>
       </c>
       <c r="F2" t="n">
         <v>1.6423</v>
@@ -610,10 +610,10 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4386</v>
+        <v>-0.1634</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9458</v>
+        <v>0.3437</v>
       </c>
       <c r="U2" t="n">
         <v>-0.5071</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.796</v>
+        <v>2.4607</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7579</v>
+        <v>3.4226</v>
       </c>
       <c r="F3" t="n">
         <v>-0.9619</v>
@@ -688,10 +688,10 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.709</v>
+        <v>-1.0443</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5432</v>
+        <v>0.2079</v>
       </c>
       <c r="U3" t="n">
         <v>-1.2522</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4477</v>
+        <v>1.0392</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8624</v>
+        <v>2.6389</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4147</v>
+        <v>-1.5996</v>
       </c>
       <c r="G4" t="n">
         <v>2.3465</v>
@@ -766,13 +766,13 @@
         <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0137</v>
+        <v>-0.3948</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3461</v>
+        <v>0.1226</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3324</v>
+        <v>-0.5173</v>
       </c>
       <c r="V4" t="n">
         <v>-1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3567</v>
+        <v>-0.4068</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6665</v>
+        <v>-0.7783</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3098</v>
+        <v>0.3715</v>
       </c>
       <c r="G5" t="n">
         <v>-4.8498</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.122</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1202</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0635</v>
+        <v>-0.0018</v>
       </c>
       <c r="V5" t="n">
         <v>2.8249</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2457</v>
+        <v>-2.1155</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7564</v>
+        <v>1.8249</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.002</v>
+        <v>-3.9404</v>
       </c>
       <c r="G7" t="n">
         <v>-0.06610000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5944</v>
+        <v>-1.4643</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1899</v>
+        <v>-0.1214</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4046</v>
+        <v>-1.3429</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8902</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>J. LOPEZ SANTANA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2865</v>
+        <v>-3.1783</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9502</v>
+        <v>-1.6451</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3363</v>
+        <v>-1.5332</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4075</v>
+        <v>-1.587</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9732</v>
+        <v>-0.3407</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5658</v>
+        <v>-1.2463</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6549</v>
+        <v>-1.4817</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1428</v>
+        <v>-0.1063</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7977</v>
+        <v>-1.3754</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0624</v>
+        <v>-0.1053</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8304</v>
+        <v>-0.2344</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.232</v>
+        <v>0.1291</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.8276</v>
+        <v>1.305</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0514</v>
+        <v>-1.2014</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.125</v>
+        <v>-0.1634</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0735</v>
+        <v>-1.038</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANTANA</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5628</v>
+        <v>-3.5331</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9371</v>
+        <v>-1.9502</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6257</v>
+        <v>-1.5829</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.587</v>
+        <v>-0.4075</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3407</v>
+        <v>-0.9732</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2463</v>
+        <v>0.5658</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4817</v>
+        <v>1.6549</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1063</v>
+        <v>-0.1428</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3754</v>
+        <v>1.7977</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1053</v>
+        <v>-2.0624</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2344</v>
+        <v>-0.8304</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1291</v>
+        <v>-1.232</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5859</v>
+        <v>-0.298</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4554</v>
+        <v>-0.125</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1304</v>
+        <v>-0.173</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2439</v>
+        <v>-4.2698</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4359</v>
+        <v>-2.5851</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8079</v>
+        <v>-1.6846</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4116</v>
@@ -1234,13 +1234,13 @@
         <v>2.3926</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7023</v>
+        <v>-0.7282</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0839</v>
+        <v>-0.2331</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.4951</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9414</v>
+        <v>-5.5878</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1797</v>
+        <v>-2.8877</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7617</v>
+        <v>-2.7001</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1365</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0224</v>
+        <v>-0.6687</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4675</v>
+        <v>-0.1754</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4933</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2751</v>
+        <v>-7.1325</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8022</v>
+        <v>-5.6905</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4729</v>
+        <v>-1.4421</v>
       </c>
       <c r="G12" t="n">
         <v>-2.641</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.632</v>
+        <v>-0.4894</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4265</v>
+        <v>-0.3957</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7395</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.2056</v>
+        <v>-20.8631</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.4544</v>
+        <v>-8.112100000000002</v>
       </c>
       <c r="F13" t="n">
         <v>-12.7509</v>
@@ -1468,13 +1468,13 @@
         <v>15.2255</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.6875</v>
+        <v>-6.345000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3664000000000003</v>
+        <v>-0.02390000000000006</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.321100000000001</v>
+        <v>-6.320999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0649</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.548999999999999</v>
+        <v>9.3635</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9098</v>
+        <v>6.5803</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6392</v>
+        <v>2.7831</v>
       </c>
       <c r="G14" t="n">
         <v>6.2861</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1111</v>
+        <v>0.9256</v>
       </c>
       <c r="T14" t="n">
-        <v>0.012</v>
+        <v>0.6826</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="V14" t="n">
         <v>2.8042</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.5446</v>
+        <v>6.9987</v>
       </c>
       <c r="E15" t="n">
-        <v>7.1309</v>
+        <v>6.3486</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4137</v>
+        <v>0.6501</v>
       </c>
       <c r="G15" t="n">
         <v>1.9789</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5005</v>
+        <v>1.9546</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1907</v>
+        <v>1.4084</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3098</v>
+        <v>0.5462</v>
       </c>
       <c r="V15" t="n">
         <v>1.3252</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1807</v>
+        <v>3.8891</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6553</v>
+        <v>3.0965</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5254</v>
+        <v>0.7926</v>
       </c>
       <c r="G16" t="n">
         <v>1.2829</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>1.788</v>
+        <v>1.4964</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6511</v>
+        <v>1.0923</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1369</v>
+        <v>0.4041</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1206</v>
+        <v>3.1251</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2816</v>
+        <v>1.9521</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8391</v>
+        <v>1.173</v>
       </c>
       <c r="G17" t="n">
         <v>1.5058</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0377</v>
+        <v>0.9668</v>
       </c>
       <c r="T17" t="n">
-        <v>0.024</v>
+        <v>0.6946</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0618</v>
+        <v>0.2722</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1552</v>
+        <v>0.8199</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9204</v>
+        <v>-0.3687</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2348</v>
+        <v>1.1885</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6721</v>
+        <v>0.0791</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0274</v>
+        <v>0.9063</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6446</v>
+        <v>-0.8272</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1327</v>
+        <v>-0.2737</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2857</v>
+        <v>1.0251</v>
       </c>
       <c r="L18" t="n">
-        <v>0.153</v>
+        <v>-1.2989</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8047</v>
+        <v>0.3529</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3131</v>
+        <v>-0.1188</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4916</v>
+        <v>0.4717</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8221000000000001</v>
+        <v>-0.0078</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0106</v>
+        <v>0.1226</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1886</v>
+        <v>-0.1304</v>
       </c>
       <c r="V18" t="n">
         <v>-0.339</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.469</v>
+        <v>-0.339</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7493</v>
+        <v>0.5154</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4959</v>
+        <v>0.2499</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2451</v>
+        <v>0.2656</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3162</v>
+        <v>0.6721</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5353</v>
+        <v>0.0274</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7809</v>
+        <v>0.6446</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.152</v>
+        <v>-0.1327</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8149</v>
+        <v>-0.2857</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3371</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8358</v>
+        <v>0.8047</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2796</v>
+        <v>0.3131</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5562</v>
+        <v>0.4916</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.0875</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.2175</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.305</v>
-      </c>
       <c r="S19" t="n">
-        <v>1.3169</v>
+        <v>0.1824</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8736</v>
+        <v>0.3401</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4433</v>
+        <v>-0.1577</v>
       </c>
       <c r="V19" t="n">
         <v>-0.339</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.339</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>P. SCRUBB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4902</v>
+        <v>0.3705</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7407</v>
+        <v>-0.7783</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2505</v>
+        <v>1.1488</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3972</v>
+        <v>-0.0297</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2099</v>
+        <v>0.5018</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1873</v>
+        <v>-0.5315</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1327</v>
+        <v>0.0669</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0944</v>
+        <v>0.3896</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>-0.3227</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2645</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1155</v>
+        <v>0.1122</v>
       </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>-0.2088</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6525</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.5676</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9094</v>
+        <v>0.8289</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6081</v>
+        <v>0.5071</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3014</v>
+        <v>0.3217</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.469</v>
+        <v>1.7464</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.2154</v>
       </c>
       <c r="X20" t="n">
         <v>-1.469</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1846</v>
+        <v>-0.0185</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0392</v>
+        <v>0.2937</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8546</v>
+        <v>-0.3122</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0791</v>
+        <v>0.3972</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9063</v>
+        <v>0.2099</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8272</v>
+        <v>0.1873</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2737</v>
+        <v>0.1327</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0251</v>
+        <v>0.0944</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2989</v>
+        <v>0.0382</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3529</v>
+        <v>0.2645</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1188</v>
+        <v>0.1155</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4717</v>
+        <v>0.149</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0123</v>
+        <v>0.4008</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.548</v>
+        <v>0.161</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4643</v>
+        <v>0.2397</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.339</v>
+        <v>-1.469</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.339</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. SCRUBB</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.0368</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6723</v>
+        <v>-1.9429</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0922</v>
+        <v>1.9061</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0297</v>
+        <v>-1.3162</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5018</v>
+        <v>-0.5353</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5315</v>
+        <v>-0.7809</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0669</v>
+        <v>-2.152</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3896</v>
+        <v>-0.8149</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3227</v>
+        <v>-1.3371</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.8358</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1122</v>
+        <v>0.2796</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2088</v>
+        <v>0.5562</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1751</v>
+        <v>1.0875</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5676</v>
+        <v>-0.2175</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1217</v>
+        <v>0.5308</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3869</v>
+        <v>0.4266</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2652</v>
+        <v>0.1042</v>
       </c>
       <c r="V22" t="n">
-        <v>1.7464</v>
+        <v>-0.339</v>
       </c>
       <c r="W22" t="n">
-        <v>3.2154</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.469</v>
+        <v>-0.339</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8375</v>
+        <v>-2.3495</v>
       </c>
       <c r="E23" t="n">
         <v>-2.6804</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1571</v>
+        <v>0.3309</v>
       </c>
       <c r="G23" t="n">
         <v>1.579</v>
@@ -2248,13 +2248,13 @@
         <v>1.9576</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4111</v>
+        <v>0.8992</v>
       </c>
       <c r="T23" t="n">
         <v>0.8857</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4746</v>
+        <v>0.0135</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>21.1874</v>
+        <v>22.67740000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>12.7509</v>
+        <v>12.7508</v>
       </c>
       <c r="F24" t="n">
-        <v>8.436500000000001</v>
+        <v>9.926500000000001</v>
       </c>
       <c r="G24" t="n">
         <v>12.4352</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3074</v>
+        <v>5.307399999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>7.1278</v>
+        <v>7.127800000000001</v>
       </c>
       <c r="J24" t="n">
         <v>12.0301</v>
@@ -2308,16 +2308,16 @@
         <v>6.781299999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4051999999999998</v>
+        <v>0.4051999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>0.05880000000000007</v>
+        <v>0.05880000000000002</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3463000000000002</v>
+        <v>0.3463000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q24" t="n">
         <v>-15.2254</v>
@@ -2326,13 +2326,13 @@
         <v>15.2254</v>
       </c>
       <c r="S24" t="n">
-        <v>6.687400000000001</v>
+        <v>8.1777</v>
       </c>
       <c r="T24" t="n">
-        <v>6.3209</v>
+        <v>6.321</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3664000000000001</v>
+        <v>1.8565</v>
       </c>
       <c r="V24" t="n">
         <v>2.0646</v>
@@ -2341,7 +2341,7 @@
         <v>9.625599999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.5609</v>
+        <v>-7.560900000000001</v>
       </c>
     </row>
   </sheetData>
